--- a/data/Documentacion_faltante.xlsx
+++ b/data/Documentacion_faltante.xlsx
@@ -919,7 +919,12 @@
           <t>URBANIZADORA Y CONSTRUCTORA CURG SA DE CV</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n"/>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>Bitácora de obra
+Finiquito (excel)</t>
+        </is>
+      </c>
       <c r="F8" s="11" t="n"/>
     </row>
     <row r="9" ht="60" customHeight="1">
@@ -3541,7 +3546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3676,6 +3681,96 @@
         </is>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>48ae1d348d0d4e2bacf20a1150ca358e</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Req_003_ULOP</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A-2510-K100188-61401-D/0528/2021</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>DIR</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>EJE_DIR_BIT.pdf</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bitácora de obra</t>
+        </is>
+      </c>
+      <c r="G4" s="28" t="n">
+        <v>46255.63350694445</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>LFAM</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>03e897659f094577882a0c7fb88e54f6</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Req_003_ULOP</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>A-2510-K100188-61401-D/0528/2021</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>DIR</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ETR_DIR_FIN.xls</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Finiquito (excel)</t>
+        </is>
+      </c>
+      <c r="G5" s="28" t="n">
+        <v>46255.63350694445</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>LFAM</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>

--- a/data/Documentacion_faltante.xlsx
+++ b/data/Documentacion_faltante.xlsx
@@ -24,8 +24,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -240,7 +241,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -330,6 +331,7 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3635,10 +3637,8 @@
           <t>DAPF</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
+      <c r="I2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -3680,10 +3680,8 @@
           <t>DAPF</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
+      <c r="I3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -3725,10 +3723,8 @@
           <t>LFAM</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
+      <c r="I4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -3770,10 +3766,8 @@
           <t>LFAM</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
+      <c r="I5" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3787,7 +3781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3820,6 +3814,32 @@
         <is>
           <t>Documentos</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>e59b21be404944e7bebd999797e37d83</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Req_003_ULOP</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="29" t="n">
+        <v>46255</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>LFAM</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/Documentacion_faltante.xlsx
+++ b/data/Documentacion_faltante.xlsx
@@ -1051,7 +1051,11 @@
           <t>CONSTRUCCION Y SERVICIOS DEL BAJIO SA DE CV</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n"/>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>Normas de calidad</t>
+        </is>
+      </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
           <t>XGOT</t>
@@ -3548,7 +3552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3768,6 +3772,51 @@
       </c>
       <c r="I5" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>c950cb7776c742df8e0c118f12c38e61</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Req_003_ULOP</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>G-5051-K100250-61401-D/0541/2022</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>DIR</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>PPP_DIR_NOC.pdf</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Normas de calidad</t>
+        </is>
+      </c>
+      <c r="G6" s="28" t="n">
+        <v>46255.68847222222</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>XGOT</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/Documentacion_faltante.xlsx
+++ b/data/Documentacion_faltante.xlsx
@@ -1053,7 +1053,8 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Normas de calidad</t>
+          <t>Normas de calidad
+Permisos de construcción, uso de suelo, ambientales, etc.</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
@@ -3552,7 +3553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3814,6 +3815,51 @@
         </is>
       </c>
       <c r="I6" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cacc753dcaa8408889edc7728a35927e</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Req_003_ULOP</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>G-5051-K100250-61401-D/0541/2022</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>DIR</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>PPP_DIR_PER.pdf</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Permisos de construcción, uso de suelo, ambientales, etc.</t>
+        </is>
+      </c>
+      <c r="G7" s="28" t="n">
+        <v>46255.91678240741</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>XGOT</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>

--- a/data/Documentacion_faltante.xlsx
+++ b/data/Documentacion_faltante.xlsx
@@ -3553,7 +3553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3860,6 +3860,51 @@
         </is>
       </c>
       <c r="I7" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>9fced7554a224c71b5e4b959356ad4e2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Req_003_ULOP</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>GD-564023</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>DIR</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>PPP_DIR_EIA.pdf</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Estudios de factibilidad y evaluación de impacto ambiental</t>
+        </is>
+      </c>
+      <c r="G8" s="28" t="n">
+        <v>46261.12668981482</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>DAPF</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>

--- a/data/Documentacion_faltante.xlsx
+++ b/data/Documentacion_faltante.xlsx
@@ -3553,7 +3553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3602,6 +3602,11 @@
           <t>Corte</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Especificacion</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3771,8 +3776,10 @@
           <t>LFAM</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>1</v>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -3979,7 +3986,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/Documentacion_faltante.xlsx
+++ b/data/Documentacion_faltante.xlsx
@@ -3553,7 +3553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3867,51 +3867,6 @@
         </is>
       </c>
       <c r="I7" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>9fced7554a224c71b5e4b959356ad4e2</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Req_003_ULOP</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>GD-564023</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>DIR</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>PPP_DIR_EIA.pdf</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Estudios de factibilidad y evaluación de impacto ambiental</t>
-        </is>
-      </c>
-      <c r="G8" s="28" t="n">
-        <v>46261.12668981482</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>DAPF</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
         <is>
           <t>PENDIENTE</t>
         </is>

--- a/data/Documentacion_faltante.xlsx
+++ b/data/Documentacion_faltante.xlsx
@@ -3647,8 +3647,10 @@
           <t>DAPF</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>1</v>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -3690,8 +3692,10 @@
           <t>DAPF</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>1</v>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -3733,8 +3737,10 @@
           <t>LFAM</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>1</v>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -3883,7 +3889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3916,32 +3922,6 @@
         <is>
           <t>Documentos</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>e59b21be404944e7bebd999797e37d83</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Req_003_ULOP</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="29" t="n">
-        <v>46255</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>LFAM</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/Documentacion_faltante.xlsx
+++ b/data/Documentacion_faltante.xlsx
@@ -921,12 +921,7 @@
           <t>URBANIZADORA Y CONSTRUCTORA CURG SA DE CV</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>Bitácora de obra
-Finiquito (excel)</t>
-        </is>
-      </c>
+      <c r="E8" s="12" t="inlineStr"/>
       <c r="F8" s="11" t="n"/>
     </row>
     <row r="9" ht="60" customHeight="1">
@@ -1051,12 +1046,7 @@
           <t>CONSTRUCCION Y SERVICIOS DEL BAJIO SA DE CV</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>Normas de calidad
-Permisos de construcción, uso de suelo, ambientales, etc.</t>
-        </is>
-      </c>
+      <c r="E13" s="12" t="inlineStr"/>
       <c r="F13" s="11" t="inlineStr">
         <is>
           <t>XGOT</t>
@@ -1087,12 +1077,7 @@
           <t>INMOBILIARIA DIMARJ, S.A. DE C.V.</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>Estudios de factibilidad y evaluación de impacto ambiental
-Documento que acredite la propiedad o posesión, o los derechos de propiedad incluyendo derechos de vía y expropiación de los inmuebles</t>
-        </is>
-      </c>
+      <c r="E14" s="12" t="inlineStr"/>
       <c r="F14" s="11" t="inlineStr">
         <is>
           <t>DAPF</t>
@@ -3553,7 +3538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3605,276 +3590,6 @@
       <c r="J1" t="inlineStr">
         <is>
           <t>Especificacion</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>24b37934b9584020ae7bd80489d72d13</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Req_003_ULOP</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>GD-564023</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>LSI</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>PPP_LSI_EIA.pdf</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Estudios de factibilidad y evaluación de impacto ambiental</t>
-        </is>
-      </c>
-      <c r="G2" s="28" t="n">
-        <v>46255.63186342592</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>DAPF</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ef4f2d6b7f6d4b47bbabc49eecb74e10</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Req_003_ULOP</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>GD-564023</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LSI</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>PPP_LSI_POS.pdf</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Documento que acredite la propiedad o posesión, o los derechos de propiedad incluyendo derechos de vía y expropiación de los inmuebles</t>
-        </is>
-      </c>
-      <c r="G3" s="28" t="n">
-        <v>46255.63186342592</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>DAPF</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>48ae1d348d0d4e2bacf20a1150ca358e</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Req_003_ULOP</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>A-2510-K100188-61401-D/0528/2021</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>DIR</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>EJE_DIR_BIT.pdf</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Bitácora de obra</t>
-        </is>
-      </c>
-      <c r="G4" s="28" t="n">
-        <v>46255.63350694445</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>LFAM</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>03e897659f094577882a0c7fb88e54f6</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Req_003_ULOP</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>A-2510-K100188-61401-D/0528/2021</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>DIR</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>ETR_DIR_FIN.xls</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Finiquito (excel)</t>
-        </is>
-      </c>
-      <c r="G5" s="28" t="n">
-        <v>46255.63350694445</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>LFAM</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>c950cb7776c742df8e0c118f12c38e61</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Req_003_ULOP</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>G-5051-K100250-61401-D/0541/2022</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>DIR</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>PPP_DIR_NOC.pdf</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Normas de calidad</t>
-        </is>
-      </c>
-      <c r="G6" s="28" t="n">
-        <v>46255.68847222222</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>XGOT</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cacc753dcaa8408889edc7728a35927e</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Req_003_ULOP</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>G-5051-K100250-61401-D/0541/2022</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>DIR</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>PPP_DIR_PER.pdf</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Permisos de construcción, uso de suelo, ambientales, etc.</t>
-        </is>
-      </c>
-      <c r="G7" s="28" t="n">
-        <v>46255.91678240741</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>XGOT</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
         </is>
       </c>
     </row>

--- a/data/Documentacion_faltante.xlsx
+++ b/data/Documentacion_faltante.xlsx
@@ -1077,7 +1077,11 @@
           <t>INMOBILIARIA DIMARJ, S.A. DE C.V.</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr"/>
+      <c r="E14" s="12" t="inlineStr">
+        <is>
+          <t>anexo de ejecución</t>
+        </is>
+      </c>
       <c r="F14" s="11" t="inlineStr">
         <is>
           <t>DAPF</t>
@@ -3538,7 +3542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3590,6 +3594,56 @@
       <c r="J1" t="inlineStr">
         <is>
           <t>Especificacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>d7c901301cf34bdc9ab98a972a26c787</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Req_003_ULOP</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>GD-564023</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>LSI</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>PPP_LSI_CNV.pdf</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Convenios de colaboración y sus anexos</t>
+        </is>
+      </c>
+      <c r="G2" s="28" t="n">
+        <v>46261.14960648148</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>DAPF</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>anexo de ejecución</t>
         </is>
       </c>
     </row>

--- a/data/Documentacion_faltante.xlsx
+++ b/data/Documentacion_faltante.xlsx
@@ -3636,10 +3636,8 @@
           <t>DAPF</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
+      <c r="I2" t="n">
+        <v>1</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -3658,7 +3656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3691,6 +3689,32 @@
         <is>
           <t>Documentos</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>3b3e551da2e1487fb6064c5d3eeec85f</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Req_003_ULOP</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="29" t="n">
+        <v>46260</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>LFAM</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/Documentacion_faltante.xlsx
+++ b/data/Documentacion_faltante.xlsx
@@ -1046,7 +1046,11 @@
           <t>CONSTRUCCION Y SERVICIOS DEL BAJIO SA DE CV</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr"/>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>Bitácora de obra</t>
+        </is>
+      </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
           <t>XGOT</t>
@@ -3542,7 +3546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3644,6 +3648,52 @@
           <t>anexo de ejecución</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>a2ede2b957124910935cb246c3052872</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Req_003_ULOP</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>G-5051-K100250-61401-D/0541/2022</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>DIR</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>EJE_DIR_BIT.pdf</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Bitácora de obra</t>
+        </is>
+      </c>
+      <c r="G3" s="28" t="n">
+        <v>46261.15150462963</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>XGOT</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Documentacion_faltante.xlsx
+++ b/data/Documentacion_faltante.xlsx
@@ -1083,7 +1083,8 @@
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>anexo de ejecución</t>
+          <t>anexo de ejecución
+Propuesta económica del ganador</t>
         </is>
       </c>
       <c r="F14" s="11" t="inlineStr">
@@ -3546,7 +3547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3693,7 +3694,52 @@
           <t>PENDIENTE</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>9225e1e18507462e8b196654ab529407</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Req_003_ULOP</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>GD-564023</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LSI</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ADJ_LSI_PEG.pdf</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Propuesta económica del ganador</t>
+        </is>
+      </c>
+      <c r="G4" s="28" t="n">
+        <v>46261.15252314815</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>DAPF</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Documentacion_faltante.xlsx
+++ b/data/Documentacion_faltante.xlsx
@@ -3689,10 +3689,8 @@
           <t>XGOT</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
+      <c r="I3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -3734,12 +3732,9 @@
           <t>DAPF</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3752,7 +3747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3811,6 +3806,32 @@
       </c>
       <c r="F2" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>eab137135eed4496856f73e34e7f4fe9</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Req_003_ULOP</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" s="29" t="n">
+        <v>46261</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>LFAM</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/Documentacion_faltante.xlsx
+++ b/data/Documentacion_faltante.xlsx
@@ -3641,8 +3641,10 @@
           <t>DAPF</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>1</v>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -3747,7 +3749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3785,7 +3787,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3b3e551da2e1487fb6064c5d3eeec85f</t>
+          <t>eab137135eed4496856f73e34e7f4fe9</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3794,10 +3796,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="29" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3805,32 +3807,6 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>eab137135eed4496856f73e34e7f4fe9</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Req_003_ULOP</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" s="29" t="n">
-        <v>46261</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>LFAM</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
         <v>2</v>
       </c>
     </row>

--- a/data/Documentacion_faltante.xlsx
+++ b/data/Documentacion_faltante.xlsx
@@ -3691,8 +3691,10 @@
           <t>XGOT</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>2</v>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -3734,8 +3736,10 @@
           <t>DAPF</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>2</v>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>PENDIENTE</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3749,7 +3753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3782,32 +3786,6 @@
         <is>
           <t>Documentos</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>eab137135eed4496856f73e34e7f4fe9</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Req_003_ULOP</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D2" s="29" t="n">
-        <v>46261</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>LFAM</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/Documentacion_faltante.xlsx
+++ b/data/Documentacion_faltante.xlsx
@@ -1046,11 +1046,7 @@
           <t>CONSTRUCCION Y SERVICIOS DEL BAJIO SA DE CV</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>Bitácora de obra</t>
-        </is>
-      </c>
+      <c r="E13" s="12" t="inlineStr"/>
       <c r="F13" s="11" t="inlineStr">
         <is>
           <t>XGOT</t>
@@ -1081,12 +1077,7 @@
           <t>INMOBILIARIA DIMARJ, S.A. DE C.V.</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
-        <is>
-          <t>anexo de ejecución
-Propuesta económica del ganador</t>
-        </is>
-      </c>
+      <c r="E14" s="12" t="inlineStr"/>
       <c r="F14" s="11" t="inlineStr">
         <is>
           <t>DAPF</t>
@@ -3547,7 +3538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3599,146 +3590,6 @@
       <c r="J1" t="inlineStr">
         <is>
           <t>Especificacion</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>d7c901301cf34bdc9ab98a972a26c787</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Req_003_ULOP</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>GD-564023</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>LSI</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>PPP_LSI_CNV.pdf</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Convenios de colaboración y sus anexos</t>
-        </is>
-      </c>
-      <c r="G2" s="28" t="n">
-        <v>46261.14960648148</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>DAPF</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>anexo de ejecución</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>a2ede2b957124910935cb246c3052872</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Req_003_ULOP</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>G-5051-K100250-61401-D/0541/2022</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>DIR</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>EJE_DIR_BIT.pdf</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Bitácora de obra</t>
-        </is>
-      </c>
-      <c r="G3" s="28" t="n">
-        <v>46261.15150462963</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>XGOT</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>9225e1e18507462e8b196654ab529407</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Req_003_ULOP</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>GD-564023</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LSI</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>ADJ_LSI_PEG.pdf</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Propuesta económica del ganador</t>
-        </is>
-      </c>
-      <c r="G4" s="28" t="n">
-        <v>46261.15252314815</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>DAPF</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>PENDIENTE</t>
         </is>
       </c>
     </row>
